--- a/ig/DM_FINESS_New/ValueSet-tre-r376-type-evenement-administratif-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-tre-r376-type-evenement-administratif-all.xlsx
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Jeu de valeurs ALL des événements affectant le cycle de vie des entités et activités enrgeistrées dans FINESS+</t>
+    <t>Jeu de valeurs ALL contenant les événements affectant le cycle de vie des entités et activités enrgeistrées dans FINESS+</t>
   </si>
   <si>
     <t>Purpose</t>
